--- a/Manufacturing/USBGE-CTRL-001_Document_Control_Register.xlsx
+++ b/Manufacturing/USBGE-CTRL-001_Document_Control_Register.xlsx
@@ -1896,7 +1896,7 @@
         <x:v>Open</x:v>
       </x:c>
       <x:c r="G6" s="9" t="str">
-        <x:v>689c3ed458aac78967d26eaa7077300db3945aa78ab8f8ea2d8f9f4597ef53c2</x:v>
+        <x:v>ff679edc2ae7ed26fbd966640b661beb843932def622e5006d3dd114bef5cb5e</x:v>
       </x:c>
       <x:c r="H6" s="9" t="str">
         <x:v>XLSX</x:v>
